--- a/docs/design/k8s-오브젝트-시방서_인프라플랫폼.xlsx
+++ b/docs/design/k8s-오브젝트-시방서_인프라플랫폼.xlsx
@@ -46,11 +46,11 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="14" hidden="1">'Certificate (TLS)'!$A$2:$F$7</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="15" hidden="1">'PodSecurity'!$A$2:$I$7</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="16" hidden="1">'Mesh (PeerAuth · Sidecar)'!$A$2:$F$8</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="17" hidden="1">'Deployment (Rollout · Pod설계)'!$A$2:$D$17</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="17" hidden="1">'Deployment (Rollout · Pod설계)'!$A$2:$D$19</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="18" hidden="1">'HTTPRoute (Canary)'!$A$2:$F$6</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="19" hidden="1">'Operator (install)'!$A$2:$E$12</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="19" hidden="1">'Operator (install)'!$A$2:$E$11</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="20" hidden="1">'ArgoCD (CI·CD)'!$A$2:$D$13</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="21" hidden="1">'Backup·DR'!$A$2:$H$15</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="21" hidden="1">'Backup·DR'!$A$2:$H$14</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -2119,7 +2119,7 @@
       </c>
       <c r="F7" s="9" t="inlineStr">
         <is>
-          <t>배포 방식은 P0 확정</t>
+          <t>DaemonSet 노드 수집</t>
         </is>
       </c>
     </row>
@@ -3569,7 +3569,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I7"/>
+  <dimension ref="A1:J7"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9.00390625" defaultRowHeight="16.4"/>
   <cols>
     <col width="14" customWidth="1" style="1" min="1" max="1"/>
@@ -3867,6 +3867,11 @@
       <c r="I7" s="9" t="inlineStr">
         <is>
           <t>DaemonSet/host 수집 방식 확정 후 예외 최소화</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>DaemonSet의 host 로그 mount 범위만 최소 예외로 정의</t>
         </is>
       </c>
     </row>
@@ -4143,7 +4148,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D17"/>
+  <dimension ref="A1:D19"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9.00390625" defaultRowHeight="16.4"/>
   <cols>
     <col width="16" customWidth="1" style="1" min="1" max="1"/>
@@ -4472,39 +4477,83 @@
       </c>
       <c r="C16" s="9" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>DaemonSet · 노드당 1</t>
         </is>
       </c>
       <c r="D16" s="9" t="inlineStr">
         <is>
-          <t>제공 구성도에 Deployment/DaemonSet 표기가 혼재 → P0 확정</t>
+          <t>노드 로그·메트릭·트레이스 수집</t>
         </is>
       </c>
     </row>
     <row r="17" ht="36" customHeight="1" s="8">
       <c r="A17" s="9" t="inlineStr">
         <is>
+          <t>observability workload</t>
+        </is>
+      </c>
+      <c r="B17" s="9" t="inlineStr">
+        <is>
+          <t>Loki · Tempo kind</t>
+        </is>
+      </c>
+      <c r="C17" s="9" t="inlineStr">
+        <is>
+          <t>StatefulSet</t>
+        </is>
+      </c>
+      <c r="D17" s="9" t="inlineStr">
+        <is>
+          <t>MinIO object storage backend 사용</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="9" t="inlineStr">
+        <is>
+          <t>observability workload</t>
+        </is>
+      </c>
+      <c r="B18" s="9" t="inlineStr">
+        <is>
+          <t>MinIO kind</t>
+        </is>
+      </c>
+      <c r="C18" s="9" t="inlineStr">
+        <is>
+          <t>StatefulSet</t>
+        </is>
+      </c>
+      <c r="D18" s="9" t="inlineStr">
+        <is>
+          <t>OpenEBS LocalPV volumeClaimTemplate 사용</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="9" t="inlineStr">
+        <is>
           <t>observability graceful</t>
         </is>
       </c>
-      <c r="B17" s="9" t="inlineStr">
+      <c r="B19" s="9" t="inlineStr">
         <is>
           <t>terminationGracePeriodSeconds/preStop</t>
         </is>
       </c>
-      <c r="C17" s="9" t="inlineStr">
+      <c r="C19" s="9" t="inlineStr">
         <is>
           <t>TBD</t>
         </is>
       </c>
-      <c r="D17" s="9" t="inlineStr">
+      <c r="D19" s="9" t="inlineStr">
         <is>
           <t>Loki·Tempo flush 및 Grafana 연결 종료시간 검증</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:D17"/>
+  <autoFilter ref="A2:D19"/>
   <mergeCells count="1">
     <mergeCell ref="A1:D1"/>
   </mergeCells>
@@ -4969,7 +5018,7 @@
       </c>
       <c r="E10" s="9" t="inlineStr">
         <is>
-          <t>관측과 내부 object storage. backup 전용 ns는 만들지 않음</t>
+          <t>관측 스택과 Loki·Tempo용 내부 object storage</t>
         </is>
       </c>
     </row>
@@ -4989,7 +5038,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E12"/>
+  <dimension ref="A1:E11"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9.00390625" defaultRowHeight="16.4"/>
   <cols>
     <col width="18" customWidth="1" style="1" min="1" max="1"/>
@@ -5225,12 +5274,12 @@
     <row r="10" ht="36" customHeight="1" s="8">
       <c r="A10" s="9" t="inlineStr">
         <is>
-          <t>Prometheus Operator</t>
+          <t>CloudNativePG</t>
         </is>
       </c>
       <c r="B10" s="9" t="inlineStr">
         <is>
-          <t>mp-observability-ns 또는 system ns TBD</t>
+          <t>mp-cnpg-system (TBD)</t>
         </is>
       </c>
       <c r="C10" s="9" t="inlineStr">
@@ -5240,24 +5289,24 @@
       </c>
       <c r="D10" s="9" t="inlineStr">
         <is>
-          <t>Prometheus · Alertmanager · ServiceMonitor · PrometheusRule</t>
+          <t>Cluster · ScheduledBackup</t>
         </is>
       </c>
       <c r="E10" s="9" t="inlineStr">
         <is>
-          <t>사용 여부/설치 chart를 P0 확정</t>
+          <t>PG Barman Cloud→S3/PITR, 데이터 담당과 공동 소관</t>
         </is>
       </c>
     </row>
     <row r="11" ht="36" customHeight="1" s="8">
       <c r="A11" s="9" t="inlineStr">
         <is>
-          <t>CloudNativePG</t>
+          <t>ECK</t>
         </is>
       </c>
       <c r="B11" s="9" t="inlineStr">
         <is>
-          <t>mp-cnpg-system (TBD)</t>
+          <t>mp-elastic-system (TBD)</t>
         </is>
       </c>
       <c r="C11" s="9" t="inlineStr">
@@ -5267,44 +5316,18 @@
       </c>
       <c r="D11" s="9" t="inlineStr">
         <is>
-          <t>Cluster · ScheduledBackup</t>
+          <t>Elasticsearch</t>
         </is>
       </c>
       <c r="E11" s="9" t="inlineStr">
         <is>
-          <t>PG Barman Cloud→S3/PITR, 데이터 담당과 공동 소관</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="36" customHeight="1" s="8">
-      <c r="A12" s="9" t="inlineStr">
-        <is>
-          <t>ECK</t>
-        </is>
-      </c>
-      <c r="B12" s="9" t="inlineStr">
-        <is>
-          <t>mp-elastic-system (TBD)</t>
-        </is>
-      </c>
-      <c r="C12" s="9" t="inlineStr">
-        <is>
-          <t>ArgoCD</t>
-        </is>
-      </c>
-      <c r="D12" s="9" t="inlineStr">
-        <is>
-          <t>Elasticsearch</t>
-        </is>
-      </c>
-      <c r="E12" s="9" t="inlineStr">
-        <is>
           <t>S3 snapshot repository/SLM은 데이터 담당과 공동 소관</t>
         </is>
       </c>
     </row>
+    <row r="12" ht="36" customHeight="1" s="8"/>
   </sheetData>
-  <autoFilter ref="A2:E12"/>
+  <autoFilter ref="A2:E11"/>
   <mergeCells count="1">
     <mergeCell ref="A1:E1"/>
   </mergeCells>
@@ -5615,7 +5638,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H15"/>
+  <dimension ref="A1:H14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" style="8" min="1" max="1"/>
@@ -6149,12 +6172,12 @@
     <row r="14" ht="42" customHeight="1" s="8">
       <c r="A14" s="12" t="inlineStr">
         <is>
-          <t>Velero</t>
+          <t>복구 순서</t>
         </is>
       </c>
       <c r="B14" s="12" t="inlineStr">
         <is>
-          <t>미도입</t>
+          <t>DR Runbook</t>
         </is>
       </c>
       <c r="C14" s="12" t="inlineStr">
@@ -6164,74 +6187,33 @@
       </c>
       <c r="D14" s="12" t="inlineStr">
         <is>
+          <t>P0/P1 복구훈련</t>
+        </is>
+      </c>
+      <c r="E14" s="12" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E14" s="12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="F14" s="12" t="inlineStr">
         <is>
-          <t>GitOps+etcd+제품별 native restore</t>
+          <t>노드→K8s/ArgoCD→operator→PG→ES→Redis→앱→smoke test</t>
         </is>
       </c>
       <c r="G14" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>백업 주체별 분리</t>
         </is>
       </c>
       <c r="H14" s="12" t="inlineStr">
         <is>
-          <t>backup namespace도 사용하지 않음</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="42" customHeight="1" s="8">
-      <c r="A15" s="12" t="inlineStr">
-        <is>
-          <t>복구 순서</t>
-        </is>
-      </c>
-      <c r="B15" s="12" t="inlineStr">
-        <is>
-          <t>DR Runbook</t>
-        </is>
-      </c>
-      <c r="C15" s="12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D15" s="12" t="inlineStr">
-        <is>
-          <t>P0/P1 복구훈련</t>
-        </is>
-      </c>
-      <c r="E15" s="12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F15" s="12" t="inlineStr">
-        <is>
-          <t>노드→K8s/ArgoCD→operator→PG→ES→Redis→앱→smoke test</t>
-        </is>
-      </c>
-      <c r="G15" s="12" t="inlineStr">
-        <is>
-          <t>백업 주체별 분리</t>
-        </is>
-      </c>
-      <c r="H15" s="12" t="inlineStr">
-        <is>
           <t>RPO/RTO는 복구시험 실측 후 확정</t>
         </is>
       </c>
     </row>
+    <row r="15" ht="42" customHeight="1" s="8"/>
   </sheetData>
-  <autoFilter ref="A2:H15"/>
+  <autoFilter ref="A2:H14"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -6920,7 +6902,7 @@
       </c>
       <c r="G7" s="9" t="inlineStr">
         <is>
-          <t>초기 생성 여부 미확정. Prometheus는 HPA가 아닌 HA replica/sharding 대상; Loki·Tempo는 배포 모드 확정 후 판단</t>
+          <t>현재 생성 계획 없음. Prometheus는 단일 StatefulSet/Host B 고정이며, 나머지 관측 구성요소의 replica 확정 후 HPA 적용 필요성을 판단</t>
         </is>
       </c>
     </row>
@@ -7511,7 +7493,7 @@
       </c>
       <c r="B13" s="9" t="inlineStr">
         <is>
-          <t>TBD (chart endpoint)</t>
+          <t>관리 HTTP :12345</t>
         </is>
       </c>
       <c r="C13" s="9" t="inlineStr">
@@ -7521,12 +7503,12 @@
       </c>
       <c r="D13" s="9" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>관리 HTTP :12345 · TBD</t>
         </is>
       </c>
       <c r="E13" s="9" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>노드당 1 DaemonSet, OTLP 중계 시 4317/4318</t>
         </is>
       </c>
       <c r="F13" s="9" t="inlineStr">

--- a/docs/design/k8s-오브젝트-시방서_인프라플랫폼.xlsx
+++ b/docs/design/k8s-오브젝트-시방서_인프라플랫폼.xlsx
@@ -8,55 +8,56 @@
   </bookViews>
   <sheets>
     <sheet name="표지" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="NameSpace" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="PriorityClass" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="ResourceQuota" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="LimitRange" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="HPA" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="PodDisruptionBudget" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="Probe (Live·Ready·Startup)" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="ConfigMap" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="Secret" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="ServiceAccount" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="Role (RBAC)" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet name="NetworkPolicy" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet name="CiliumNetworkPolicy" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet name="Certificate (TLS)" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet name="PodSecurity" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet name="Mesh (PeerAuth · Sidecar)" sheetId="17" state="visible" r:id="rId17"/>
-    <sheet name="Deployment (Rollout · Pod설계)" sheetId="18" state="visible" r:id="rId18"/>
-    <sheet name="Deployment (Monitoring)" sheetId="19" state="visible" r:id="rId19"/>
-    <sheet name="StatefulSet (Monitoring)" sheetId="20" state="visible" r:id="rId20"/>
-    <sheet name="DaemonSet (Monitoring)" sheetId="21" state="visible" r:id="rId21"/>
-    <sheet name="Service (Monitoring)" sheetId="22" state="visible" r:id="rId22"/>
-    <sheet name="Storage (Monitoring)" sheetId="23" state="visible" r:id="rId23"/>
-    <sheet name="StorageClass" sheetId="24" state="visible" r:id="rId24"/>
-    <sheet name="Backup · DR" sheetId="25" state="visible" r:id="rId25"/>
-    <sheet name="HTTPRoute (Canary)" sheetId="26" state="visible" r:id="rId26"/>
-    <sheet name="Operator (install)" sheetId="27" state="visible" r:id="rId27"/>
-    <sheet name="ArgoCD (CI·CD)" sheetId="28" state="visible" r:id="rId28"/>
+    <sheet name="보안 개요 (심층방어)" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="NameSpace" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="PriorityClass" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="ResourceQuota" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="LimitRange" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="HPA" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="PodDisruptionBudget" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="Probe (Live·Ready·Startup)" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="ConfigMap" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="Secret" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="ServiceAccount" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="Role (RBAC)" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="NetworkPolicy" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="CiliumNetworkPolicy" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet name="Certificate (TLS)" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet name="PodSecurity" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet name="Mesh (PeerAuth · Sidecar)" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet name="Deployment (Rollout · Pod설계)" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet name="Deployment (Monitoring)" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet name="StatefulSet (Monitoring)" sheetId="21" state="visible" r:id="rId21"/>
+    <sheet name="DaemonSet (Monitoring)" sheetId="22" state="visible" r:id="rId22"/>
+    <sheet name="Service (Monitoring)" sheetId="23" state="visible" r:id="rId23"/>
+    <sheet name="Storage (Monitoring)" sheetId="24" state="visible" r:id="rId24"/>
+    <sheet name="StorageClass" sheetId="25" state="visible" r:id="rId25"/>
+    <sheet name="Backup · DR" sheetId="26" state="visible" r:id="rId26"/>
+    <sheet name="HTTPRoute (Canary)" sheetId="27" state="visible" r:id="rId27"/>
+    <sheet name="Operator (install)" sheetId="28" state="visible" r:id="rId28"/>
+    <sheet name="ArgoCD (CI·CD)" sheetId="29" state="visible" r:id="rId29"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'NameSpace'!$A$2:$E$9</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'PriorityClass'!$A$2:$E$3</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'ResourceQuota'!$A$2:$G$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'LimitRange'!$A$2:$G$3</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'HPA'!$A$2:$G$6</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'PodDisruptionBudget'!$A$2:$E$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Probe (Live·Ready·Startup)'!$A$2:$F$5</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'ConfigMap'!$A$2:$E$11</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'Secret'!$A$2:$F$11</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'ServiceAccount'!$A$1:$F$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'Role (RBAC)'!$A$2:$H$6</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="12" hidden="1">'NetworkPolicy'!$A$2:$F$9</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="13" hidden="1">'CiliumNetworkPolicy'!$A$2:$E$3</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="14" hidden="1">'Certificate (TLS)'!$A$2:$F$6</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="15" hidden="1">'PodSecurity'!$A$2:$I$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="16" hidden="1">'Mesh (PeerAuth · Sidecar)'!$A$2:$F$7</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="17" hidden="1">'Deployment (Rollout · Pod설계)'!$A$2:$D$12</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="25" hidden="1">'HTTPRoute (Canary)'!$A$2:$F$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="26" hidden="1">'Operator (install)'!$A$2:$E$8</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="27" hidden="1">'ArgoCD (CI·CD)'!$A$2:$D$9</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'NameSpace'!$A$2:$E$9</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'PriorityClass'!$A$2:$E$3</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'ResourceQuota'!$A$2:$G$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'LimitRange'!$A$2:$G$3</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'HPA'!$A$2:$G$6</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'PodDisruptionBudget'!$A$2:$E$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'Probe (Live·Ready·Startup)'!$A$2:$F$5</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'ConfigMap'!$A$2:$E$11</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'Secret'!$A$2:$F$11</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'ServiceAccount'!$A$1:$F$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="12" hidden="1">'Role (RBAC)'!$A$2:$H$6</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="13" hidden="1">'NetworkPolicy'!$A$2:$F$9</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="14" hidden="1">'CiliumNetworkPolicy'!$A$2:$E$3</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="15" hidden="1">'Certificate (TLS)'!$A$2:$F$6</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="16" hidden="1">'PodSecurity'!$A$2:$I$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="17" hidden="1">'Mesh (PeerAuth · Sidecar)'!$A$2:$F$7</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="18" hidden="1">'Deployment (Rollout · Pod설계)'!$A$2:$D$12</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="26" hidden="1">'HTTPRoute (Canary)'!$A$2:$F$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="27" hidden="1">'Operator (install)'!$A$2:$E$8</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="28" hidden="1">'ArgoCD (CI·CD)'!$A$2:$D$9</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -65,7 +66,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="9">
+  <fonts count="11">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -115,6 +116,17 @@
       <name val="맑은 고딕"/>
       <b val="1"/>
       <color rgb="00000000"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="맑은 고딕"/>
+      <color rgb="00555555"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="맑은 고딕"/>
+      <b val="1"/>
+      <color rgb="00C00000"/>
       <sz val="10"/>
     </font>
   </fonts>
@@ -186,7 +198,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -214,6 +226,8 @@
     <xf numFmtId="0" fontId="8" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -594,7 +608,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -616,8 +629,13 @@
         </is>
       </c>
     </row>
-    <row r="6"/>
-    <row r="7"/>
+    <row r="6">
+      <c r="A6" s="11" t="inlineStr">
+        <is>
+          <t>★ '보안 개요 (심층방어)' 시트 = 레이어별 보안 요약 (발표용 한눈표) · 상세는 각 Kind 시트</t>
+        </is>
+      </c>
+    </row>
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
@@ -1046,6 +1064,562 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E21"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="26" customWidth="1" min="4" max="4"/>
+    <col width="34" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="5" t="inlineStr">
+        <is>
+          <t>configMapGenerator 해시 접미사(mp-app-common-&lt;hash&gt;)로 내용 변경 시 자동 롤아웃. env 주입(volume 아님) → 갱신 시 파드 재시작.</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="3" t="inlineStr">
+        <is>
+          <t>이름</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>NS</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>key</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>value (예)</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>비고</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>mp-app-common</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>mp-app-ns</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>PGHOST</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>mp-pg-rw.mp-data-ns.svc</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>IP→Service DNS (환경 무관)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>mp-app-common</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>mp-app-ns</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>ESHOST</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>mp-es.mp-data-ns.svc</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>mp-app-common</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>mp-app-ns</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>REDISHOST</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>mp-redis.mp-data-ns.svc</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>mp-app-common</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>mp-app-ns</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>OTEL_EXPORTER_OTLP_ENDPOINT</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>(관측 콜렉터)</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>전 서비스 공유</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>mp-app-common</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>mp-app-ns</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>ENVIRONMENT</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>production</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>mp-app-common</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>mp-app-ns</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>LOG_LEVEL</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>mp-chat-config</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>mp-app-ns</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>CHAT_*_ENABLED</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>서비스별 기능 플래그</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>mp-chat-config</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>mp-app-ns</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>MONTHLY_CAP_ENABLED</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="E10" s="4" t="inlineStr">
+        <is>
+          <t>Gemini 월 예산 캡</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>mp-mealplan-config</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>mp-app-ns</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>RANKING_ML_ENABLED</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>true / false</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>서비스별 분리(전체 롤아웃 방지)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="34" customHeight="1">
+      <c r="A12" s="7" t="inlineStr">
+        <is>
+          <t>mp-grafana-provisioning</t>
+        </is>
+      </c>
+      <c r="B12" s="7" t="inlineStr">
+        <is>
+          <t>mp-observability-ns</t>
+        </is>
+      </c>
+      <c r="C12" s="7" t="inlineStr">
+        <is>
+          <t>datasources</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>Prometheus/Loki/Tempo Service DNS</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
+        <is>
+          <t>UID는 dashboard JSON과 고정</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="34" customHeight="1">
+      <c r="A13" s="7" t="inlineStr">
+        <is>
+          <t>mp-grafana-dashboards</t>
+        </is>
+      </c>
+      <c r="B13" s="7" t="inlineStr">
+        <is>
+          <t>mp-observability-ns</t>
+        </is>
+      </c>
+      <c r="C13" s="7" t="inlineStr">
+        <is>
+          <t>dashboards</t>
+        </is>
+      </c>
+      <c r="D13" s="7" t="inlineStr">
+        <is>
+          <t>GitOps→ConfigMap</t>
+        </is>
+      </c>
+      <c r="E13" s="7" t="inlineStr">
+        <is>
+          <t>기존 dashboard JSON 승계</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="34" customHeight="1">
+      <c r="A14" s="7" t="inlineStr">
+        <is>
+          <t>mp-prometheus-config</t>
+        </is>
+      </c>
+      <c r="B14" s="7" t="inlineStr">
+        <is>
+          <t>mp-observability-ns</t>
+        </is>
+      </c>
+      <c r="C14" s="7" t="inlineStr">
+        <is>
+          <t>scrape_configs</t>
+        </is>
+      </c>
+      <c r="D14" s="7" t="inlineStr">
+        <is>
+          <t>K8s·Hubble·Istio·app·kube-state-metrics</t>
+        </is>
+      </c>
+      <c r="E14" s="7" t="inlineStr">
+        <is>
+          <t>메트릭은 Prometheus가 직접 scrape</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="34" customHeight="1">
+      <c r="A15" s="7" t="inlineStr">
+        <is>
+          <t>mp-prometheus-rules</t>
+        </is>
+      </c>
+      <c r="B15" s="7" t="inlineStr">
+        <is>
+          <t>mp-observability-ns</t>
+        </is>
+      </c>
+      <c r="C15" s="7" t="inlineStr">
+        <is>
+          <t>rule_files</t>
+        </is>
+      </c>
+      <c r="D15" s="7" t="inlineStr">
+        <is>
+          <t>기존 alert-rules 20개</t>
+        </is>
+      </c>
+      <c r="E15" s="7" t="inlineStr">
+        <is>
+          <t>사고 이력 규칙 승계</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="34" customHeight="1">
+      <c r="A16" s="7" t="inlineStr">
+        <is>
+          <t>mp-loki-config</t>
+        </is>
+      </c>
+      <c r="B16" s="7" t="inlineStr">
+        <is>
+          <t>mp-observability-ns</t>
+        </is>
+      </c>
+      <c r="C16" s="7" t="inlineStr">
+        <is>
+          <t>storage</t>
+        </is>
+      </c>
+      <c r="D16" s="7" t="inlineStr">
+        <is>
+          <t>http://mp-minio-api.mp-data-ns.svc.cluster.local:9000 / bucket=loki</t>
+        </is>
+      </c>
+      <c r="E16" s="7" t="inlineStr">
+        <is>
+          <t>cross-namespace S3 endpoint · single-binary · TSDB index</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="34" customHeight="1">
+      <c r="A17" s="7" t="inlineStr">
+        <is>
+          <t>mp-loki-config</t>
+        </is>
+      </c>
+      <c r="B17" s="7" t="inlineStr">
+        <is>
+          <t>mp-observability-ns</t>
+        </is>
+      </c>
+      <c r="C17" s="7" t="inlineStr">
+        <is>
+          <t>retention</t>
+        </is>
+      </c>
+      <c r="D17" s="7" t="inlineStr">
+        <is>
+          <t>168h</t>
+        </is>
+      </c>
+      <c r="E17" s="7" t="inlineStr">
+        <is>
+          <t>compactor retention</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="34" customHeight="1">
+      <c r="A18" s="7" t="inlineStr">
+        <is>
+          <t>mp-tempo-config</t>
+        </is>
+      </c>
+      <c r="B18" s="7" t="inlineStr">
+        <is>
+          <t>mp-observability-ns</t>
+        </is>
+      </c>
+      <c r="C18" s="7" t="inlineStr">
+        <is>
+          <t>receiver/storage</t>
+        </is>
+      </c>
+      <c r="D18" s="7" t="inlineStr">
+        <is>
+          <t>OTLP 4317/4318 · http://mp-minio-api.mp-data-ns.svc.cluster.local:9000 / bucket=tempo</t>
+        </is>
+      </c>
+      <c r="E18" s="7" t="inlineStr">
+        <is>
+          <t>cross-namespace S3 endpoint · monolithic · WAL=emptyDir(P0 검증)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="34" customHeight="1">
+      <c r="A19" s="7" t="inlineStr">
+        <is>
+          <t>mp-alloy-config</t>
+        </is>
+      </c>
+      <c r="B19" s="7" t="inlineStr">
+        <is>
+          <t>mp-observability-ns</t>
+        </is>
+      </c>
+      <c r="C19" s="7" t="inlineStr">
+        <is>
+          <t>collect/write</t>
+        </is>
+      </c>
+      <c r="D19" s="7" t="inlineStr">
+        <is>
+          <t>logs→Loki · traces→Tempo</t>
+        </is>
+      </c>
+      <c r="E19" s="7" t="inlineStr">
+        <is>
+          <t>메트릭 중복 scrape 금지</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="34" customHeight="1">
+      <c r="A20" s="7" t="inlineStr">
+        <is>
+          <t>mp-alertmanager-config</t>
+        </is>
+      </c>
+      <c r="B20" s="7" t="inlineStr">
+        <is>
+          <t>mp-observability-ns</t>
+        </is>
+      </c>
+      <c r="C20" s="7" t="inlineStr">
+        <is>
+          <t>route</t>
+        </is>
+      </c>
+      <c r="D20" s="7" t="inlineStr">
+        <is>
+          <t>Slack receiver; webhook은 Secret</t>
+        </is>
+      </c>
+      <c r="E20" s="7" t="inlineStr">
+        <is>
+          <t>기존 route 승계</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="34" customHeight="1">
+      <c r="A21" s="7" t="inlineStr">
+        <is>
+          <t>mp-minio-config</t>
+        </is>
+      </c>
+      <c r="B21" s="7" t="inlineStr">
+        <is>
+          <t>mp-data-ns</t>
+        </is>
+      </c>
+      <c r="C21" s="7" t="inlineStr">
+        <is>
+          <t>buckets</t>
+        </is>
+      </c>
+      <c r="D21" s="7" t="inlineStr">
+        <is>
+          <t>loki·tempo·ranking-models 분리</t>
+        </is>
+      </c>
+      <c r="E21" s="7" t="inlineStr">
+        <is>
+          <t>실제 bucket 생성 주체는 Helm/init 단계에서 확정</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A2:E11"/>
+  <mergeCells count="1">
+    <mergeCell ref="A1:E1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1602,7 +2176,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1913,7 +2487,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2284,7 +2858,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2889,7 +3463,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2975,7 +3549,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3168,7 +3742,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3533,7 +4107,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3822,7 +4396,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4087,7 +4661,434 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H10"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="4" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="4" max="4"/>
+    <col width="64" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="12" t="inlineStr">
+        <is>
+          <t>심층 방어(Defense-in-Depth) — 레이어별 보안 오브젝트·역할 한눈 요약 (상세는 각 Kind 시트 참조)  ·  주황 = 정본 미반영(신규 제안)  ·  차단(prevent) 6층 = 정본 확정 + 거버넌스·감사 2층 = 신규</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="3" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>레이어</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>막는 위협</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>K8s 오브젝트</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>보안 역할 (구체)</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>오퍼레이터·도구</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>정본 근거</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>상태</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>네트워크 격리</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>횡적 이동(lateral movement)
+유출 파드 egress</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>NetworkPolicy
+CiliumNetworkPolicy</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>default-deny 화이트리스트 — 정책 붙는 순간 미명시 트래픽 전부 차단
+frontend egress=DNS만(털려도 나갈 곳 0)
+Gemini FQDN egress(표준 불가 → Cilium DNS프록시 학습)
+CoreDNS·istiod·kubelet probe 예외 필수(누락 시 클러스터 다운)</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>Cilium
+(+Hubble)</t>
+        </is>
+      </c>
+      <c r="G3" s="4" t="inlineStr">
+        <is>
+          <t>§10.1~10.4</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
+          <t>확정</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>신원·권한 (RBAC)</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>토큰 탈취
+API 오남용</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>ServiceAccount
+Role/RoleBinding</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>앱 SA 권한 0 + automountServiceAccountToken:false(안 쓰는 토큰=공격면 제거)
+ArgoCD만 클러스터 전역 쓰기 → ns 격리
+Jenkins 클러스터 권한 0(config 레포 커밋만)</t>
+        </is>
+      </c>
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t>내장 K8s
+(GitOps=ArgoCD)</t>
+        </is>
+      </c>
+      <c r="G4" s="4" t="inlineStr">
+        <is>
+          <t>§10.6</t>
+        </is>
+      </c>
+      <c r="H4" s="4" t="inlineStr">
+        <is>
+          <t>확정</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>파드 하드닝</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>컨테이너 탈출(escape)
+특권 상승(privesc)</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>SecurityContext(필드)
+PodSecurity(PSS)</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>runAsNonRoot · cap drop ALL · readOnlyRootFS · allowPrivEsc=false · seccomp RuntimeDefault
+PSS restricted = 미충족 파드 배포 거부
+(app·pipeline만; data·*-system 제외 — 오퍼레이터·CNI 특권 필요)</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>내장 admission</t>
+        </is>
+      </c>
+      <c r="G5" s="4" t="inlineStr">
+        <is>
+          <t>§10.5·§10.7</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
+          <t>확정</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>메시 (전송 암호화)</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>도청(평문 통신)
+서비스 위장</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>PeerAuthentication
+AuthorizationPolicy</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>mTLS PERMISSIVE→STRICT(ns 단위 · data ns 평문 유지)
+L7 인가(누가 누구를 호출 가능)
+Istio CNI plugin(restricted의 NET_ADMIN 금지와 충돌 회피)</t>
+        </is>
+      </c>
+      <c r="F6" s="4" t="inlineStr">
+        <is>
+          <t>Istio</t>
+        </is>
+      </c>
+      <c r="G6" s="4" t="inlineStr">
+        <is>
+          <t>§11.2·§11.3</t>
+        </is>
+      </c>
+      <c r="H6" s="4" t="inlineStr">
+        <is>
+          <t>확정</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>비밀·인증서</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>git에 비밀 노출
+인증서 만료</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>ExternalSecret/SecretStore
+Certificate/Issuer</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>외부 저장소→Secret 동기화(레포에 평문 비밀 0)
+TLS 인증서 자동 발급·갱신</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>ESO
+cert-manager</t>
+        </is>
+      </c>
+      <c r="G7" s="4" t="inlineStr">
+        <is>
+          <t>plan §6.4</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
+        <is>
+          <t>확정</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>공급망 (이미지)</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>취약·위조 이미지 배포</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>CI 게이트 (Trivy)</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t>Trivy CRITICAL 게이트 — 이미지 내 SW를 CVE DB와 대조, 발견 시 빌드 실패(--exit-code 1)
+Harbor 3태그(:sha 불변 신원 + :X.Y.Z 릴리스 핀)</t>
+        </is>
+      </c>
+      <c r="F8" s="4" t="inlineStr">
+        <is>
+          <t>Trivy
+(CI/Jenkins)</t>
+        </is>
+      </c>
+      <c r="G8" s="4" t="inlineStr">
+        <is>
+          <t>plan §463·480</t>
+        </is>
+      </c>
+      <c r="H8" s="4" t="inlineStr">
+        <is>
+          <t>확정</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>거버넌스·정책강제</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>설정 드리프트
+실수 배포·규칙 누락</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>Kyverno ClusterPolicy
+(validate·mutate·generate)</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>readOnlyRootFS 강제(PSS 사각지대 보완)
+새 ns에 default-deny NetworkPolicy 자동 생성(§10.2 함정 제거)
+레지스트리 Harbor 제한 · :latest 차단(3태그 정책 강제)
+resources 필수화(미기재 배포 거부)
+automountServiceAccountToken:false 자동 주입</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>Kyverno</t>
+        </is>
+      </c>
+      <c r="G9" s="4" t="inlineStr">
+        <is>
+          <t>신규 (§10 확장)</t>
+        </is>
+      </c>
+      <c r="H9" s="6" t="inlineStr">
+        <is>
+          <t>신규</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>감사 (CIS)</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>클러스터 설정 미스구성</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>kube-bench Job/CronJob</t>
+        </is>
+      </c>
+      <c r="E10" s="4" t="inlineStr">
+        <is>
+          <t>CIS 벤치마크로 control plane·kubelet·etcd 설정 점검(PASS/FAIL/WARN + remediation)
+kubeadm 자체관리라 전 범위 대상(EKS 이식 시 control plane은 AWS 몫)
+주기 CronJob 또는 1회 스냅샷</t>
+        </is>
+      </c>
+      <c r="F10" s="4" t="inlineStr">
+        <is>
+          <t>kube-bench
+(도구)</t>
+        </is>
+      </c>
+      <c r="G10" s="4" t="inlineStr">
+        <is>
+          <t>신규 (§10 확장)</t>
+        </is>
+      </c>
+      <c r="H10" s="6" t="inlineStr">
+        <is>
+          <t>신규</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4273,336 +5274,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:E12"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="20" customWidth="1" min="1" max="1"/>
-    <col width="26" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="40" customWidth="1" min="5" max="5"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="5" t="inlineStr">
-        <is>
-          <t>네임스페이스 = 정책(주입 라벨·PSS·NetworkPolicy)이 붙는 경계. 데이터·파이프라인·관측 ns는 각 도메인 담당 소관.</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="3" t="inlineStr">
-        <is>
-          <t>ns</t>
-        </is>
-      </c>
-      <c r="B2" s="3" t="inlineStr">
-        <is>
-          <t>용도</t>
-        </is>
-      </c>
-      <c r="C2" s="3" t="inlineStr">
-        <is>
-          <t>istio-injection</t>
-        </is>
-      </c>
-      <c r="D2" s="3" t="inlineStr">
-        <is>
-          <t>PodSecurity</t>
-        </is>
-      </c>
-      <c r="E2" s="3" t="inlineStr">
-        <is>
-          <t>비고</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="4" t="inlineStr">
-        <is>
-          <t>mp-app-ns</t>
-        </is>
-      </c>
-      <c r="B3" s="4" t="inlineStr">
-        <is>
-          <t>FastAPI 9 + frontend</t>
-        </is>
-      </c>
-      <c r="C3" s="4" t="inlineStr">
-        <is>
-          <t>enabled</t>
-        </is>
-      </c>
-      <c r="D3" s="4" t="inlineStr">
-        <is>
-          <t>restricted</t>
-        </is>
-      </c>
-      <c r="E3" s="4" t="inlineStr">
-        <is>
-          <t>메시 경계 · L7 관측 · 카나리 대상</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="4" t="inlineStr">
-        <is>
-          <t>mp-argocd-ns</t>
-        </is>
-      </c>
-      <c r="B4" s="4" t="inlineStr">
-        <is>
-          <t>ArgoCD (CD)</t>
-        </is>
-      </c>
-      <c r="C4" s="4" t="inlineStr">
-        <is>
-          <t>disabled</t>
-        </is>
-      </c>
-      <c r="D4" s="4" t="inlineStr">
-        <is>
-          <t>baseline</t>
-        </is>
-      </c>
-      <c r="E4" s="4" t="inlineStr">
-        <is>
-          <t>클러스터 전역 쓰기 → RBAC 격리</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="4" t="inlineStr">
-        <is>
-          <t>mp-istio-system</t>
-        </is>
-      </c>
-      <c r="B5" s="4" t="inlineStr">
-        <is>
-          <t>Istio operator</t>
-        </is>
-      </c>
-      <c r="C5" s="4" t="inlineStr">
-        <is>
-          <t>disabled</t>
-        </is>
-      </c>
-      <c r="D5" s="4" t="inlineStr">
-        <is>
-          <t>privileged</t>
-        </is>
-      </c>
-      <c r="E5" s="4" t="inlineStr">
-        <is>
-          <t>사이드카 주입 webhook</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="4" t="inlineStr">
-        <is>
-          <t>mp-metallb-system</t>
-        </is>
-      </c>
-      <c r="B6" s="4" t="inlineStr">
-        <is>
-          <t>MetalLB</t>
-        </is>
-      </c>
-      <c r="C6" s="4" t="inlineStr">
-        <is>
-          <t>disabled</t>
-        </is>
-      </c>
-      <c r="D6" s="4" t="inlineStr">
-        <is>
-          <t>privileged</t>
-        </is>
-      </c>
-      <c r="E6" s="4" t="inlineStr">
-        <is>
-          <t>LoadBalancer IPAM</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="4" t="inlineStr">
-        <is>
-          <t>mp-cert-manager</t>
-        </is>
-      </c>
-      <c r="B7" s="4" t="inlineStr">
-        <is>
-          <t>cert-manager</t>
-        </is>
-      </c>
-      <c r="C7" s="4" t="inlineStr">
-        <is>
-          <t>disabled</t>
-        </is>
-      </c>
-      <c r="D7" s="4" t="inlineStr">
-        <is>
-          <t>privileged</t>
-        </is>
-      </c>
-      <c r="E7" s="4" t="inlineStr">
-        <is>
-          <t>TLS 발급</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="4" t="inlineStr">
-        <is>
-          <t>mp-external-secrets</t>
-        </is>
-      </c>
-      <c r="B8" s="4" t="inlineStr">
-        <is>
-          <t>External Secrets Operator</t>
-        </is>
-      </c>
-      <c r="C8" s="4" t="inlineStr">
-        <is>
-          <t>disabled</t>
-        </is>
-      </c>
-      <c r="D8" s="4" t="inlineStr">
-        <is>
-          <t>privileged</t>
-        </is>
-      </c>
-      <c r="E8" s="4" t="inlineStr">
-        <is>
-          <t>비밀 동기화</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="4" t="inlineStr">
-        <is>
-          <t>kube-system</t>
-        </is>
-      </c>
-      <c r="B9" s="4" t="inlineStr">
-        <is>
-          <t>Cilium (CNI)</t>
-        </is>
-      </c>
-      <c r="C9" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D9" s="4" t="inlineStr">
-        <is>
-          <t>privileged</t>
-        </is>
-      </c>
-      <c r="E9" s="4" t="inlineStr">
-        <is>
-          <t>코어 CNI · eBPF (ns 고정)</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="34" customHeight="1">
-      <c r="A10" s="7" t="inlineStr">
-        <is>
-          <t>mp-data-ns</t>
-        </is>
-      </c>
-      <c r="B10" s="7" t="inlineStr">
-        <is>
-          <t>PostgreSQL·Elasticsearch·Redis·Kafka·MinIO</t>
-        </is>
-      </c>
-      <c r="C10" s="7" t="inlineStr">
-        <is>
-          <t>disabled</t>
-        </is>
-      </c>
-      <c r="D10" s="7" t="inlineStr">
-        <is>
-          <t>baseline (워크로드별 securityContext 강화)</t>
-        </is>
-      </c>
-      <c r="E10" s="7" t="inlineStr">
-        <is>
-          <t>데이터 티어와 공용 오브젝트 스토리지</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="34" customHeight="1">
-      <c r="A11" s="7" t="inlineStr">
-        <is>
-          <t>mp-observability-ns</t>
-        </is>
-      </c>
-      <c r="B11" s="7" t="inlineStr">
-        <is>
-          <t>Prometheus·Alertmanager·Grafana·Loki·Tempo·Alloy·kube-state-metrics</t>
-        </is>
-      </c>
-      <c r="C11" s="7" t="inlineStr">
-        <is>
-          <t>disabled</t>
-        </is>
-      </c>
-      <c r="D11" s="7" t="inlineStr">
-        <is>
-          <t>baseline (워크로드별 securityContext 강화)</t>
-        </is>
-      </c>
-      <c r="E11" s="7" t="inlineStr">
-        <is>
-          <t>관측이 앱 자원을 고갈시키지 않도록 격리</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="34" customHeight="1">
-      <c r="A12" s="7" t="inlineStr">
-        <is>
-          <t>mp-openebs-ns</t>
-        </is>
-      </c>
-      <c r="B12" s="7" t="inlineStr">
-        <is>
-          <t>OpenEBS LVM LocalPV CSI</t>
-        </is>
-      </c>
-      <c r="C12" s="7" t="inlineStr">
-        <is>
-          <t>disabled</t>
-        </is>
-      </c>
-      <c r="D12" s="7" t="inlineStr">
-        <is>
-          <t>privileged</t>
-        </is>
-      </c>
-      <c r="E12" s="7" t="inlineStr">
-        <is>
-          <t>스토리지 프로비저너 시스템 Namespace</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <autoFilter ref="A2:E9"/>
-  <mergeCells count="1">
-    <mergeCell ref="A1:E1"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4939,156 +5611,6 @@
       <c r="J7" s="10" t="inlineStr">
         <is>
           <t>Loki·Tempo·ranking-models 공용 오브젝트 저장소</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="34" customHeight="1"/>
-    <row r="13" ht="34" customHeight="1"/>
-    <row r="14" ht="34" customHeight="1"/>
-    <row r="15" ht="34" customHeight="1"/>
-    <row r="16" ht="34" customHeight="1"/>
-    <row r="17" ht="34" customHeight="1"/>
-    <row r="18" ht="34" customHeight="1"/>
-    <row r="19" ht="34" customHeight="1"/>
-    <row r="20" ht="34" customHeight="1"/>
-    <row r="21" ht="34" customHeight="1"/>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:J1"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:J3"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="25" customWidth="1" min="1" max="1"/>
-    <col width="24" customWidth="1" min="2" max="2"/>
-    <col width="23" customWidth="1" min="3" max="3"/>
-    <col width="35" customWidth="1" min="4" max="4"/>
-    <col width="20" customWidth="1" min="5" max="5"/>
-    <col width="25" customWidth="1" min="6" max="6"/>
-    <col width="25" customWidth="1" min="7" max="7"/>
-    <col width="31" customWidth="1" min="8" max="8"/>
-    <col width="28" customWidth="1" min="9" max="9"/>
-    <col width="46" customWidth="1" min="10" max="10"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="8" t="inlineStr">
-        <is>
-          <t>Alloy는 노드마다 1 Pod. DaemonSet→Pod이며 ReplicaSet은 없다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="9" t="inlineStr">
-        <is>
-          <t>이름</t>
-        </is>
-      </c>
-      <c r="B2" s="9" t="inlineStr">
-        <is>
-          <t>NS</t>
-        </is>
-      </c>
-      <c r="C2" s="9" t="inlineStr">
-        <is>
-          <t>배치</t>
-        </is>
-      </c>
-      <c r="D2" s="9" t="inlineStr">
-        <is>
-          <t>image</t>
-        </is>
-      </c>
-      <c r="E2" s="9" t="inlineStr">
-        <is>
-          <t>ports</t>
-        </is>
-      </c>
-      <c r="F2" s="9" t="inlineStr">
-        <is>
-          <t>ConfigMap</t>
-        </is>
-      </c>
-      <c r="G2" s="9" t="inlineStr">
-        <is>
-          <t>ServiceAccount</t>
-        </is>
-      </c>
-      <c r="H2" s="9" t="inlineStr">
-        <is>
-          <t>host mount</t>
-        </is>
-      </c>
-      <c r="I2" s="9" t="inlineStr">
-        <is>
-          <t>Service</t>
-        </is>
-      </c>
-      <c r="J2" s="9" t="inlineStr">
-        <is>
-          <t>비고</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="34" customHeight="1">
-      <c r="A3" s="10" t="inlineStr">
-        <is>
-          <t>mp-alloy</t>
-        </is>
-      </c>
-      <c r="B3" s="10" t="inlineStr">
-        <is>
-          <t>mp-observability-ns</t>
-        </is>
-      </c>
-      <c r="C3" s="10" t="inlineStr">
-        <is>
-          <t>모든 worker 노드</t>
-        </is>
-      </c>
-      <c r="D3" s="10" t="inlineStr">
-        <is>
-          <t>grafana/alloy:&lt;버전 고정&gt;</t>
-        </is>
-      </c>
-      <c r="E3" s="10" t="inlineStr">
-        <is>
-          <t>12345,4317,4318</t>
-        </is>
-      </c>
-      <c r="F3" s="10" t="inlineStr">
-        <is>
-          <t>mp-alloy-config</t>
-        </is>
-      </c>
-      <c r="G3" s="10" t="inlineStr">
-        <is>
-          <t>mp-alloy-sa</t>
-        </is>
-      </c>
-      <c r="H3" s="10" t="inlineStr">
-        <is>
-          <t>/var/log/pods readOnly</t>
-        </is>
-      </c>
-      <c r="I3" s="10" t="inlineStr">
-        <is>
-          <t>mp-alloy-http/otlp</t>
-        </is>
-      </c>
-      <c r="J3" s="10" t="inlineStr">
-        <is>
-          <t>로그 수집·OTLP trace 수신; 메트릭 중복 scrape 금지</t>
         </is>
       </c>
     </row>
@@ -5116,6 +5638,156 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:J3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="25" customWidth="1" min="1" max="1"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="23" customWidth="1" min="3" max="3"/>
+    <col width="35" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="25" customWidth="1" min="6" max="6"/>
+    <col width="25" customWidth="1" min="7" max="7"/>
+    <col width="31" customWidth="1" min="8" max="8"/>
+    <col width="28" customWidth="1" min="9" max="9"/>
+    <col width="46" customWidth="1" min="10" max="10"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" s="8" t="inlineStr">
+        <is>
+          <t>Alloy는 노드마다 1 Pod. DaemonSet→Pod이며 ReplicaSet은 없다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="9" t="inlineStr">
+        <is>
+          <t>이름</t>
+        </is>
+      </c>
+      <c r="B2" s="9" t="inlineStr">
+        <is>
+          <t>NS</t>
+        </is>
+      </c>
+      <c r="C2" s="9" t="inlineStr">
+        <is>
+          <t>배치</t>
+        </is>
+      </c>
+      <c r="D2" s="9" t="inlineStr">
+        <is>
+          <t>image</t>
+        </is>
+      </c>
+      <c r="E2" s="9" t="inlineStr">
+        <is>
+          <t>ports</t>
+        </is>
+      </c>
+      <c r="F2" s="9" t="inlineStr">
+        <is>
+          <t>ConfigMap</t>
+        </is>
+      </c>
+      <c r="G2" s="9" t="inlineStr">
+        <is>
+          <t>ServiceAccount</t>
+        </is>
+      </c>
+      <c r="H2" s="9" t="inlineStr">
+        <is>
+          <t>host mount</t>
+        </is>
+      </c>
+      <c r="I2" s="9" t="inlineStr">
+        <is>
+          <t>Service</t>
+        </is>
+      </c>
+      <c r="J2" s="9" t="inlineStr">
+        <is>
+          <t>비고</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="34" customHeight="1">
+      <c r="A3" s="10" t="inlineStr">
+        <is>
+          <t>mp-alloy</t>
+        </is>
+      </c>
+      <c r="B3" s="10" t="inlineStr">
+        <is>
+          <t>mp-observability-ns</t>
+        </is>
+      </c>
+      <c r="C3" s="10" t="inlineStr">
+        <is>
+          <t>모든 worker 노드</t>
+        </is>
+      </c>
+      <c r="D3" s="10" t="inlineStr">
+        <is>
+          <t>grafana/alloy:&lt;버전 고정&gt;</t>
+        </is>
+      </c>
+      <c r="E3" s="10" t="inlineStr">
+        <is>
+          <t>12345,4317,4318</t>
+        </is>
+      </c>
+      <c r="F3" s="10" t="inlineStr">
+        <is>
+          <t>mp-alloy-config</t>
+        </is>
+      </c>
+      <c r="G3" s="10" t="inlineStr">
+        <is>
+          <t>mp-alloy-sa</t>
+        </is>
+      </c>
+      <c r="H3" s="10" t="inlineStr">
+        <is>
+          <t>/var/log/pods readOnly</t>
+        </is>
+      </c>
+      <c r="I3" s="10" t="inlineStr">
+        <is>
+          <t>mp-alloy-http/otlp</t>
+        </is>
+      </c>
+      <c r="J3" s="10" t="inlineStr">
+        <is>
+          <t>로그 수집·OTLP trace 수신; 메트릭 중복 scrape 금지</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="34" customHeight="1"/>
+    <row r="13" ht="34" customHeight="1"/>
+    <row r="14" ht="34" customHeight="1"/>
+    <row r="15" ht="34" customHeight="1"/>
+    <row r="16" ht="34" customHeight="1"/>
+    <row r="17" ht="34" customHeight="1"/>
+    <row r="18" ht="34" customHeight="1"/>
+    <row r="19" ht="34" customHeight="1"/>
+    <row r="20" ht="34" customHeight="1"/>
+    <row r="21" ht="34" customHeight="1"/>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:J1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:G16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -5703,7 +6375,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -5957,7 +6629,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -6107,7 +6779,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -6469,7 +7141,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -6598,7 +7270,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -6846,7 +7518,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -7120,6 +7792,335 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E12"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="40" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="5" t="inlineStr">
+        <is>
+          <t>네임스페이스 = 정책(주입 라벨·PSS·NetworkPolicy)이 붙는 경계. 데이터·파이프라인·관측 ns는 각 도메인 담당 소관.</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="3" t="inlineStr">
+        <is>
+          <t>ns</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>용도</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>istio-injection</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>PodSecurity</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>비고</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>mp-app-ns</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>FastAPI 9 + frontend</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>enabled</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>restricted</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>메시 경계 · L7 관측 · 카나리 대상</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>mp-argocd-ns</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>ArgoCD (CD)</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>disabled</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>클러스터 전역 쓰기 → RBAC 격리</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>mp-istio-system</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>Istio operator</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>disabled</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>privileged</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>사이드카 주입 webhook</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>mp-metallb-system</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>MetalLB</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>disabled</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>privileged</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>LoadBalancer IPAM</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>mp-cert-manager</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>cert-manager</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>disabled</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>privileged</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>TLS 발급</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>mp-external-secrets</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>External Secrets Operator</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>disabled</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>privileged</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t>비밀 동기화</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>kube-system</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>Cilium (CNI)</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>privileged</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>코어 CNI · eBPF (ns 고정)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="34" customHeight="1">
+      <c r="A10" s="7" t="inlineStr">
+        <is>
+          <t>mp-data-ns</t>
+        </is>
+      </c>
+      <c r="B10" s="7" t="inlineStr">
+        <is>
+          <t>PostgreSQL·Elasticsearch·Redis·Kafka·MinIO</t>
+        </is>
+      </c>
+      <c r="C10" s="7" t="inlineStr">
+        <is>
+          <t>disabled</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="inlineStr">
+        <is>
+          <t>baseline (워크로드별 securityContext 강화)</t>
+        </is>
+      </c>
+      <c r="E10" s="7" t="inlineStr">
+        <is>
+          <t>데이터 티어와 공용 오브젝트 스토리지</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="34" customHeight="1">
+      <c r="A11" s="7" t="inlineStr">
+        <is>
+          <t>mp-observability-ns</t>
+        </is>
+      </c>
+      <c r="B11" s="7" t="inlineStr">
+        <is>
+          <t>Prometheus·Alertmanager·Grafana·Loki·Tempo·Alloy·kube-state-metrics</t>
+        </is>
+      </c>
+      <c r="C11" s="7" t="inlineStr">
+        <is>
+          <t>disabled</t>
+        </is>
+      </c>
+      <c r="D11" s="7" t="inlineStr">
+        <is>
+          <t>baseline (워크로드별 securityContext 강화)</t>
+        </is>
+      </c>
+      <c r="E11" s="7" t="inlineStr">
+        <is>
+          <t>관측이 앱 자원을 고갈시키지 않도록 격리</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="34" customHeight="1">
+      <c r="A12" s="7" t="inlineStr">
+        <is>
+          <t>mp-openebs-ns</t>
+        </is>
+      </c>
+      <c r="B12" s="7" t="inlineStr">
+        <is>
+          <t>OpenEBS LVM LocalPV CSI</t>
+        </is>
+      </c>
+      <c r="C12" s="7" t="inlineStr">
+        <is>
+          <t>disabled</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>privileged</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
+        <is>
+          <t>스토리지 프로비저너 시스템 Namespace</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A2:E9"/>
+  <mergeCells count="1">
+    <mergeCell ref="A1:E1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -7205,7 +8206,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -7387,7 +8388,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -7532,7 +8533,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -7788,7 +8789,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -7901,7 +8902,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -8316,560 +9317,4 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:E21"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="20" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="26" customWidth="1" min="3" max="3"/>
-    <col width="26" customWidth="1" min="4" max="4"/>
-    <col width="34" customWidth="1" min="5" max="5"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="5" t="inlineStr">
-        <is>
-          <t>configMapGenerator 해시 접미사(mp-app-common-&lt;hash&gt;)로 내용 변경 시 자동 롤아웃. env 주입(volume 아님) → 갱신 시 파드 재시작.</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="3" t="inlineStr">
-        <is>
-          <t>이름</t>
-        </is>
-      </c>
-      <c r="B2" s="3" t="inlineStr">
-        <is>
-          <t>NS</t>
-        </is>
-      </c>
-      <c r="C2" s="3" t="inlineStr">
-        <is>
-          <t>key</t>
-        </is>
-      </c>
-      <c r="D2" s="3" t="inlineStr">
-        <is>
-          <t>value (예)</t>
-        </is>
-      </c>
-      <c r="E2" s="3" t="inlineStr">
-        <is>
-          <t>비고</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="4" t="inlineStr">
-        <is>
-          <t>mp-app-common</t>
-        </is>
-      </c>
-      <c r="B3" s="4" t="inlineStr">
-        <is>
-          <t>mp-app-ns</t>
-        </is>
-      </c>
-      <c r="C3" s="4" t="inlineStr">
-        <is>
-          <t>PGHOST</t>
-        </is>
-      </c>
-      <c r="D3" s="4" t="inlineStr">
-        <is>
-          <t>mp-pg-rw.mp-data-ns.svc</t>
-        </is>
-      </c>
-      <c r="E3" s="4" t="inlineStr">
-        <is>
-          <t>IP→Service DNS (환경 무관)</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="4" t="inlineStr">
-        <is>
-          <t>mp-app-common</t>
-        </is>
-      </c>
-      <c r="B4" s="4" t="inlineStr">
-        <is>
-          <t>mp-app-ns</t>
-        </is>
-      </c>
-      <c r="C4" s="4" t="inlineStr">
-        <is>
-          <t>ESHOST</t>
-        </is>
-      </c>
-      <c r="D4" s="4" t="inlineStr">
-        <is>
-          <t>mp-es.mp-data-ns.svc</t>
-        </is>
-      </c>
-      <c r="E4" s="4" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="4" t="inlineStr">
-        <is>
-          <t>mp-app-common</t>
-        </is>
-      </c>
-      <c r="B5" s="4" t="inlineStr">
-        <is>
-          <t>mp-app-ns</t>
-        </is>
-      </c>
-      <c r="C5" s="4" t="inlineStr">
-        <is>
-          <t>REDISHOST</t>
-        </is>
-      </c>
-      <c r="D5" s="4" t="inlineStr">
-        <is>
-          <t>mp-redis.mp-data-ns.svc</t>
-        </is>
-      </c>
-      <c r="E5" s="4" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="4" t="inlineStr">
-        <is>
-          <t>mp-app-common</t>
-        </is>
-      </c>
-      <c r="B6" s="4" t="inlineStr">
-        <is>
-          <t>mp-app-ns</t>
-        </is>
-      </c>
-      <c r="C6" s="4" t="inlineStr">
-        <is>
-          <t>OTEL_EXPORTER_OTLP_ENDPOINT</t>
-        </is>
-      </c>
-      <c r="D6" s="4" t="inlineStr">
-        <is>
-          <t>(관측 콜렉터)</t>
-        </is>
-      </c>
-      <c r="E6" s="4" t="inlineStr">
-        <is>
-          <t>전 서비스 공유</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="4" t="inlineStr">
-        <is>
-          <t>mp-app-common</t>
-        </is>
-      </c>
-      <c r="B7" s="4" t="inlineStr">
-        <is>
-          <t>mp-app-ns</t>
-        </is>
-      </c>
-      <c r="C7" s="4" t="inlineStr">
-        <is>
-          <t>ENVIRONMENT</t>
-        </is>
-      </c>
-      <c r="D7" s="4" t="inlineStr">
-        <is>
-          <t>production</t>
-        </is>
-      </c>
-      <c r="E7" s="4" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="4" t="inlineStr">
-        <is>
-          <t>mp-app-common</t>
-        </is>
-      </c>
-      <c r="B8" s="4" t="inlineStr">
-        <is>
-          <t>mp-app-ns</t>
-        </is>
-      </c>
-      <c r="C8" s="4" t="inlineStr">
-        <is>
-          <t>LOG_LEVEL</t>
-        </is>
-      </c>
-      <c r="D8" s="4" t="inlineStr">
-        <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="E8" s="4" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="4" t="inlineStr">
-        <is>
-          <t>mp-chat-config</t>
-        </is>
-      </c>
-      <c r="B9" s="4" t="inlineStr">
-        <is>
-          <t>mp-app-ns</t>
-        </is>
-      </c>
-      <c r="C9" s="4" t="inlineStr">
-        <is>
-          <t>CHAT_*_ENABLED</t>
-        </is>
-      </c>
-      <c r="D9" s="4" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
-      </c>
-      <c r="E9" s="4" t="inlineStr">
-        <is>
-          <t>서비스별 기능 플래그</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="4" t="inlineStr">
-        <is>
-          <t>mp-chat-config</t>
-        </is>
-      </c>
-      <c r="B10" s="4" t="inlineStr">
-        <is>
-          <t>mp-app-ns</t>
-        </is>
-      </c>
-      <c r="C10" s="4" t="inlineStr">
-        <is>
-          <t>MONTHLY_CAP_ENABLED</t>
-        </is>
-      </c>
-      <c r="D10" s="4" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
-      </c>
-      <c r="E10" s="4" t="inlineStr">
-        <is>
-          <t>Gemini 월 예산 캡</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="4" t="inlineStr">
-        <is>
-          <t>mp-mealplan-config</t>
-        </is>
-      </c>
-      <c r="B11" s="4" t="inlineStr">
-        <is>
-          <t>mp-app-ns</t>
-        </is>
-      </c>
-      <c r="C11" s="4" t="inlineStr">
-        <is>
-          <t>RANKING_ML_ENABLED</t>
-        </is>
-      </c>
-      <c r="D11" s="4" t="inlineStr">
-        <is>
-          <t>true / false</t>
-        </is>
-      </c>
-      <c r="E11" s="4" t="inlineStr">
-        <is>
-          <t>서비스별 분리(전체 롤아웃 방지)</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="34" customHeight="1">
-      <c r="A12" s="7" t="inlineStr">
-        <is>
-          <t>mp-grafana-provisioning</t>
-        </is>
-      </c>
-      <c r="B12" s="7" t="inlineStr">
-        <is>
-          <t>mp-observability-ns</t>
-        </is>
-      </c>
-      <c r="C12" s="7" t="inlineStr">
-        <is>
-          <t>datasources</t>
-        </is>
-      </c>
-      <c r="D12" s="7" t="inlineStr">
-        <is>
-          <t>Prometheus/Loki/Tempo Service DNS</t>
-        </is>
-      </c>
-      <c r="E12" s="7" t="inlineStr">
-        <is>
-          <t>UID는 dashboard JSON과 고정</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="34" customHeight="1">
-      <c r="A13" s="7" t="inlineStr">
-        <is>
-          <t>mp-grafana-dashboards</t>
-        </is>
-      </c>
-      <c r="B13" s="7" t="inlineStr">
-        <is>
-          <t>mp-observability-ns</t>
-        </is>
-      </c>
-      <c r="C13" s="7" t="inlineStr">
-        <is>
-          <t>dashboards</t>
-        </is>
-      </c>
-      <c r="D13" s="7" t="inlineStr">
-        <is>
-          <t>GitOps→ConfigMap</t>
-        </is>
-      </c>
-      <c r="E13" s="7" t="inlineStr">
-        <is>
-          <t>기존 dashboard JSON 승계</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="34" customHeight="1">
-      <c r="A14" s="7" t="inlineStr">
-        <is>
-          <t>mp-prometheus-config</t>
-        </is>
-      </c>
-      <c r="B14" s="7" t="inlineStr">
-        <is>
-          <t>mp-observability-ns</t>
-        </is>
-      </c>
-      <c r="C14" s="7" t="inlineStr">
-        <is>
-          <t>scrape_configs</t>
-        </is>
-      </c>
-      <c r="D14" s="7" t="inlineStr">
-        <is>
-          <t>K8s·Hubble·Istio·app·kube-state-metrics</t>
-        </is>
-      </c>
-      <c r="E14" s="7" t="inlineStr">
-        <is>
-          <t>메트릭은 Prometheus가 직접 scrape</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="34" customHeight="1">
-      <c r="A15" s="7" t="inlineStr">
-        <is>
-          <t>mp-prometheus-rules</t>
-        </is>
-      </c>
-      <c r="B15" s="7" t="inlineStr">
-        <is>
-          <t>mp-observability-ns</t>
-        </is>
-      </c>
-      <c r="C15" s="7" t="inlineStr">
-        <is>
-          <t>rule_files</t>
-        </is>
-      </c>
-      <c r="D15" s="7" t="inlineStr">
-        <is>
-          <t>기존 alert-rules 20개</t>
-        </is>
-      </c>
-      <c r="E15" s="7" t="inlineStr">
-        <is>
-          <t>사고 이력 규칙 승계</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="34" customHeight="1">
-      <c r="A16" s="7" t="inlineStr">
-        <is>
-          <t>mp-loki-config</t>
-        </is>
-      </c>
-      <c r="B16" s="7" t="inlineStr">
-        <is>
-          <t>mp-observability-ns</t>
-        </is>
-      </c>
-      <c r="C16" s="7" t="inlineStr">
-        <is>
-          <t>storage</t>
-        </is>
-      </c>
-      <c r="D16" s="7" t="inlineStr">
-        <is>
-          <t>http://mp-minio-api.mp-data-ns.svc.cluster.local:9000 / bucket=loki</t>
-        </is>
-      </c>
-      <c r="E16" s="7" t="inlineStr">
-        <is>
-          <t>cross-namespace S3 endpoint · single-binary · TSDB index</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="34" customHeight="1">
-      <c r="A17" s="7" t="inlineStr">
-        <is>
-          <t>mp-loki-config</t>
-        </is>
-      </c>
-      <c r="B17" s="7" t="inlineStr">
-        <is>
-          <t>mp-observability-ns</t>
-        </is>
-      </c>
-      <c r="C17" s="7" t="inlineStr">
-        <is>
-          <t>retention</t>
-        </is>
-      </c>
-      <c r="D17" s="7" t="inlineStr">
-        <is>
-          <t>168h</t>
-        </is>
-      </c>
-      <c r="E17" s="7" t="inlineStr">
-        <is>
-          <t>compactor retention</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="34" customHeight="1">
-      <c r="A18" s="7" t="inlineStr">
-        <is>
-          <t>mp-tempo-config</t>
-        </is>
-      </c>
-      <c r="B18" s="7" t="inlineStr">
-        <is>
-          <t>mp-observability-ns</t>
-        </is>
-      </c>
-      <c r="C18" s="7" t="inlineStr">
-        <is>
-          <t>receiver/storage</t>
-        </is>
-      </c>
-      <c r="D18" s="7" t="inlineStr">
-        <is>
-          <t>OTLP 4317/4318 · http://mp-minio-api.mp-data-ns.svc.cluster.local:9000 / bucket=tempo</t>
-        </is>
-      </c>
-      <c r="E18" s="7" t="inlineStr">
-        <is>
-          <t>cross-namespace S3 endpoint · monolithic · WAL=emptyDir(P0 검증)</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="34" customHeight="1">
-      <c r="A19" s="7" t="inlineStr">
-        <is>
-          <t>mp-alloy-config</t>
-        </is>
-      </c>
-      <c r="B19" s="7" t="inlineStr">
-        <is>
-          <t>mp-observability-ns</t>
-        </is>
-      </c>
-      <c r="C19" s="7" t="inlineStr">
-        <is>
-          <t>collect/write</t>
-        </is>
-      </c>
-      <c r="D19" s="7" t="inlineStr">
-        <is>
-          <t>logs→Loki · traces→Tempo</t>
-        </is>
-      </c>
-      <c r="E19" s="7" t="inlineStr">
-        <is>
-          <t>메트릭 중복 scrape 금지</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="34" customHeight="1">
-      <c r="A20" s="7" t="inlineStr">
-        <is>
-          <t>mp-alertmanager-config</t>
-        </is>
-      </c>
-      <c r="B20" s="7" t="inlineStr">
-        <is>
-          <t>mp-observability-ns</t>
-        </is>
-      </c>
-      <c r="C20" s="7" t="inlineStr">
-        <is>
-          <t>route</t>
-        </is>
-      </c>
-      <c r="D20" s="7" t="inlineStr">
-        <is>
-          <t>Slack receiver; webhook은 Secret</t>
-        </is>
-      </c>
-      <c r="E20" s="7" t="inlineStr">
-        <is>
-          <t>기존 route 승계</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="34" customHeight="1">
-      <c r="A21" s="7" t="inlineStr">
-        <is>
-          <t>mp-minio-config</t>
-        </is>
-      </c>
-      <c r="B21" s="7" t="inlineStr">
-        <is>
-          <t>mp-data-ns</t>
-        </is>
-      </c>
-      <c r="C21" s="7" t="inlineStr">
-        <is>
-          <t>buckets</t>
-        </is>
-      </c>
-      <c r="D21" s="7" t="inlineStr">
-        <is>
-          <t>loki·tempo·ranking-models 분리</t>
-        </is>
-      </c>
-      <c r="E21" s="7" t="inlineStr">
-        <is>
-          <t>실제 bucket 생성 주체는 Helm/init 단계에서 확정</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <autoFilter ref="A2:E11"/>
-  <mergeCells count="1">
-    <mergeCell ref="A1:E1"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
 </file>